--- a/dev/StructureDefinition-bc-location-relationship-type-extension.xlsx
+++ b/dev/StructureDefinition-bc-location-relationship-type-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1241,7 +1241,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>102</v>
       </c>
@@ -1346,12 +1346,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK6">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
